--- a/outputs/butter/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/butter/silpo_novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08225840900715364</v>
+        <v>0.08225840900720094</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>2.681802621264837e-12</v>
+        <v>2.681802621266499e-12</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.300695796395212e-20</v>
+        <v>1.300695796394998e-20</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05640422694264773</v>
+        <v>0.05640422694264767</v>
       </c>
       <c r="C3" t="n">
         <v>0.01</v>
@@ -580,7 +580,7 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.926918418202639e-13</v>
+        <v>1.926918418201579e-13</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -618,19 +618,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009658462541496323</v>
+        <v>0.009658462541496344</v>
       </c>
       <c r="C4" t="n">
         <v>0.01527572425324723</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004241747553426809</v>
+        <v>0.0004241747553426683</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001610099236555224</v>
+        <v>0.001610099236555213</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -942,22 +942,22 @@
         <v>218</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2127764229425361</v>
+        <v>-0.2127764229425364</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2740532058530188</v>
+        <v>0.2740532058530208</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8083252331134957</v>
+        <v>-0.8083252331134949</v>
       </c>
       <c r="M2" t="n">
-        <v>1.252374581737896e-26</v>
+        <v>1.252374581588286e-26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7873814868471209</v>
+        <v>0.787381486847105</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2011263550434567</v>
+        <v>0.2011263550434396</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -1024,10 +1024,10 @@
         <v>51</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3808399108271916</v>
+        <v>0.3808399108271803</v>
       </c>
       <c r="K3" t="n">
-        <v>5.038120798935976</v>
+        <v>5.038120798935989</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -1098,16 +1098,16 @@
         <v>49</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.01931753309263347</v>
+        <v>-0.01931753309263352</v>
       </c>
       <c r="K4" t="n">
         <v>-0.1130442477150289</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5842642909954745</v>
+        <v>-0.5842642909954743</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007904731650635205</v>
+        <v>0.007904731650635162</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -1176,22 +1176,22 @@
         <v>49</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03764617386887498</v>
+        <v>0.03764617386887585</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8051638051994185</v>
+        <v>-0.8051638051994188</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.934681111534598</v>
+        <v>-0.9346811115345983</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001243423671678406</v>
+        <v>0.001243423671676451</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9262473301905363</v>
+        <v>0.9262473301905156</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3206536900888561</v>
+        <v>0.3206536900886913</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3043740439991276</v>
+        <v>0.3043740439991278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5287391650637272</v>
+        <v>0.5287391650637225</v>
       </c>
       <c r="G2" t="n">
         <v>4.220381385301966e-84</v>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1517137359967815</v>
+        <v>0.151713735996841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9428759814198608</v>
+        <v>0.9428759814198081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1216394133775718</v>
+        <v>0.1216394133775761</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7561861082620147</v>
+        <v>0.7561861082620142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1308148001577336</v>
+        <v>0.1308148001577329</v>
       </c>
       <c r="G4" t="n">
-        <v>1.441168862516734e-05</v>
+        <v>1.4411688625167e-05</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4526018945159763</v>
+        <v>0.4526018945159781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1773413029580827</v>
+        <v>0.1773413029580844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0008392768825094401</v>
+        <v>0.0008392768825093986</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -57495,10 +57495,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5437076425441756</v>
+        <v>-0.5437076425441754</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3309312196016395</v>
+        <v>-0.330931219601639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57511,10 +57511,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4804346363943778</v>
+        <v>-0.4804346363943776</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2924196897746271</v>
+        <v>-0.2924196897746266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57527,10 +57527,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4877979195156134</v>
+        <v>-0.4877979195156132</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2969014002986514</v>
+        <v>-0.2969014002986509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57543,10 +57543,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4869410305889973</v>
+        <v>-0.4869410305889971</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2963798492381931</v>
+        <v>-0.2963798492381926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57559,10 +57559,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.4870407495079181</v>
+        <v>-0.4870407495079179</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2964405438116616</v>
+        <v>-0.2964405438116611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57575,10 +57575,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4870291448967697</v>
+        <v>-0.4870291448967695</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2964334805890401</v>
+        <v>-0.2964334805890396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57591,10 +57591,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4870304953626729</v>
+        <v>-0.4870304953626727</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2964343025589618</v>
+        <v>-0.2964343025589613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57607,10 +57607,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4870303382046146</v>
+        <v>-0.4870303382046144</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2964342069036797</v>
+        <v>-0.2964342069036792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57623,10 +57623,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.487030356493603</v>
+        <v>-0.4870303564936028</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2964342180353924</v>
+        <v>-0.2964342180353919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57639,10 +57639,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4870303543652547</v>
+        <v>-0.4870303543652544</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2964342167399592</v>
+        <v>-0.2964342167399587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57655,10 +57655,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4870303546129374</v>
+        <v>-0.4870303546129372</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2964342168907129</v>
+        <v>-0.2964342168907124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57671,10 +57671,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4870303545841138</v>
+        <v>-0.4870303545841136</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2964342168731692</v>
+        <v>-0.2964342168731687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57687,10 +57687,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.4870303545874681</v>
+        <v>-0.4870303545874679</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2964342168752108</v>
+        <v>-0.2964342168752103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57703,10 +57703,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4870303545870777</v>
+        <v>-0.4870303545870775</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2964342168749732</v>
+        <v>-0.2964342168749727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57719,10 +57719,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.4870303545871231</v>
+        <v>-0.487030354587123</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2964342168750009</v>
+        <v>-0.2964342168750004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57735,10 +57735,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4870303545871179</v>
+        <v>-0.4870303545871176</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2964342168749977</v>
+        <v>-0.2964342168749972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57751,10 +57751,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4870303545871185</v>
+        <v>-0.4870303545871183</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57767,10 +57767,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57783,10 +57783,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57799,10 +57799,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57815,10 +57815,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4870303545871184</v>
+        <v>-0.4870303545871182</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.296434216874998</v>
+        <v>-0.2964342168749975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57831,10 +57831,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1255821795721559</v>
+        <v>0.1255821795721564</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08793600570328097</v>
+        <v>0.08793600570328057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57847,10 +57847,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1096819858073925</v>
+        <v>0.1096819858073931</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07680226416172616</v>
+        <v>0.07680226416172593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57863,10 +57863,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1116951389682816</v>
+        <v>0.1116951389682821</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07821192792485428</v>
+        <v>0.07821192792485403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57879,10 +57879,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>0.111440249895283</v>
+        <v>0.1114402498952836</v>
       </c>
       <c r="C26" t="n">
-        <v>0.07803344776904504</v>
+        <v>0.07803344776904479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57895,10 +57895,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1114725218757743</v>
+        <v>0.1114725218757748</v>
       </c>
       <c r="C27" t="n">
-        <v>0.07805604547415097</v>
+        <v>0.07805604547415072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57911,10 +57911,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1114684358601888</v>
+        <v>0.1114684358601894</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07805318433659908</v>
+        <v>0.07805318433659882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57927,10 +57927,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>0.111468953198236</v>
+        <v>0.1114689531982365</v>
       </c>
       <c r="C29" t="n">
-        <v>0.07805354659055594</v>
+        <v>0.07805354659055569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -57943,10 +57943,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1114688876971018</v>
+        <v>0.1114688876971024</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07805350072490745</v>
+        <v>0.07805350072490719</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -57959,10 +57959,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1114688959903225</v>
+        <v>0.111468895990323</v>
       </c>
       <c r="C31" t="n">
-        <v>0.07805350653204267</v>
+        <v>0.07805350653204242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -57975,10 +57975,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1114688949403023</v>
+        <v>0.1114688949403029</v>
       </c>
       <c r="C32" t="n">
-        <v>0.07805350579679046</v>
+        <v>0.0780535057967902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -57991,10 +57991,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1114688950732474</v>
+        <v>0.1114688950732479</v>
       </c>
       <c r="C33" t="n">
-        <v>0.07805350588988211</v>
+        <v>0.07805350588988186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -58007,10 +58007,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1114688950564149</v>
+        <v>0.1114688950564155</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07805350587809561</v>
+        <v>0.07805350587809534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -58023,10 +58023,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1114688950585461</v>
+        <v>0.1114688950585467</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07805350587958791</v>
+        <v>0.07805350587958766</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -58039,10 +58039,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1114688950582763</v>
+        <v>0.1114688950582769</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07805350587939897</v>
+        <v>0.07805350587939872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -58055,10 +58055,10 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1114688950583105</v>
+        <v>0.111468895058311</v>
       </c>
       <c r="C37" t="n">
-        <v>0.07805350587942289</v>
+        <v>0.07805350587942264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -58071,10 +58071,10 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1114688950583061</v>
+        <v>0.1114688950583067</v>
       </c>
       <c r="C38" t="n">
-        <v>0.07805350587941987</v>
+        <v>0.07805350587941962</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -58087,10 +58087,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1114688950583067</v>
+        <v>0.1114688950583072</v>
       </c>
       <c r="C39" t="n">
-        <v>0.07805350587942024</v>
+        <v>0.07805350587941999</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -58103,10 +58103,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1114688950583066</v>
+        <v>0.1114688950583072</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0780535058794202</v>
+        <v>0.07805350587941995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -58119,10 +58119,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1114688950583066</v>
+        <v>0.1114688950583072</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0780535058794202</v>
+        <v>0.07805350587941995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -58135,10 +58135,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1114688950583066</v>
+        <v>0.1114688950583072</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0780535058794202</v>
+        <v>0.07805350587941995</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -58151,10 +58151,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1114688950583066</v>
+        <v>0.1114688950583072</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0780535058794202</v>
+        <v>0.07805350587941995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
